--- a/artfynd/A 36451-2024 artfynd.xlsx
+++ b/artfynd/A 36451-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820157</v>
+        <v>119820156</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662398</v>
+        <v>662417</v>
       </c>
       <c r="R2" t="n">
-        <v>7316203</v>
+        <v>7315882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820155</v>
+        <v>119820157</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662417</v>
+        <v>662398</v>
       </c>
       <c r="R3" t="n">
-        <v>7315882</v>
+        <v>7316203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820156</v>
+        <v>119820155</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 36451-2024 artfynd.xlsx
+++ b/artfynd/A 36451-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820157</v>
+        <v>119820155</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662398</v>
+        <v>662417</v>
       </c>
       <c r="R3" t="n">
-        <v>7316203</v>
+        <v>7315882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820155</v>
+        <v>119820157</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662417</v>
+        <v>662398</v>
       </c>
       <c r="R4" t="n">
-        <v>7315882</v>
+        <v>7316203</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36451-2024 artfynd.xlsx
+++ b/artfynd/A 36451-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119820156</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820155</v>
+        <v>119820157</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662417</v>
+        <v>662398</v>
       </c>
       <c r="R3" t="n">
-        <v>7315882</v>
+        <v>7316203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820157</v>
+        <v>119820155</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>91850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662398</v>
+        <v>662417</v>
       </c>
       <c r="R4" t="n">
-        <v>7316203</v>
+        <v>7315882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36451-2024 artfynd.xlsx
+++ b/artfynd/A 36451-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820156</v>
+        <v>119820157</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662417</v>
+        <v>662398</v>
       </c>
       <c r="R2" t="n">
-        <v>7315882</v>
+        <v>7316203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820157</v>
+        <v>119820156</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662398</v>
+        <v>662417</v>
       </c>
       <c r="R3" t="n">
-        <v>7316203</v>
+        <v>7315882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 36451-2024 artfynd.xlsx
+++ b/artfynd/A 36451-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820157</v>
+        <v>119820155</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662398</v>
+        <v>662417</v>
       </c>
       <c r="R2" t="n">
-        <v>7316203</v>
+        <v>7315882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820155</v>
+        <v>119820157</v>
       </c>
       <c r="B4" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662417</v>
+        <v>662398</v>
       </c>
       <c r="R4" t="n">
-        <v>7315882</v>
+        <v>7316203</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36451-2024 artfynd.xlsx
+++ b/artfynd/A 36451-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>119820155</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820156</v>
+        <v>119820157</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662417</v>
+        <v>662398</v>
       </c>
       <c r="R3" t="n">
-        <v>7315882</v>
+        <v>7316203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820157</v>
+        <v>119820156</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662398</v>
+        <v>662417</v>
       </c>
       <c r="R4" t="n">
-        <v>7316203</v>
+        <v>7315882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36451-2024 artfynd.xlsx
+++ b/artfynd/A 36451-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820155</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820157</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820156</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>